--- a/results/Int Task Remove ACC -0.3/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.3/Linea_fi_explain.xlsx
@@ -1169,10 +1169,10 @@
         <v>-0.0004276421339060043</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0003370028723019303</v>
+        <v>-0.0003337781060974798</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0346657822030124</v>
+        <v>0.03467214960192995</v>
       </c>
       <c r="K3" t="n">
         <v>0.02262650745802448</v>
@@ -1187,7 +1187,7 @@
         <v>0.007865152895370254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03122376926718964</v>
+        <v>0.03122704153782701</v>
       </c>
       <c r="P3" t="n">
         <v>0.008931230083503827</v>
@@ -1208,7 +1208,7 @@
         <v>0.1198657099278875</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0003303767455532624</v>
+        <v>-0.0003370028723019303</v>
       </c>
       <c r="W3" t="n">
         <v>0.005113701580417569</v>
@@ -1232,13 +1232,13 @@
         <v>0.03996772414137571</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1242999713116086</v>
+        <v>0.1242968057528875</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2071687126686952</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0865618857313069</v>
+        <v>0.08655848437076268</v>
       </c>
       <c r="AG3" t="n">
         <v>0.1069231286120434</v>
@@ -1304,7 +1304,7 @@
         <v>-0.003557709206041565</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0008247215496614404</v>
+        <v>0.0008215599941761423</v>
       </c>
       <c r="BC3" t="n">
         <v>-0.0009116960623639748</v>
@@ -1373,10 +1373,10 @@
         <v>2.448627712150816e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0005396292692075199</v>
+        <v>-0.00053642516795792</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0005332414684991493</v>
+        <v>-0.0005364455697487491</v>
       </c>
       <c r="CA3" t="n">
         <v>-7.279033880003309e-06</v>
@@ -1394,7 +1394,7 @@
         <v>0.0009386042026958853</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.004969699187046659</v>
+        <v>-0.00496653763156136</v>
       </c>
       <c r="CG3" t="n">
         <v>-0.004367466045070689</v>
@@ -1440,10 +1440,10 @@
         <v>0.00227287904379635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006714080708202641</v>
+        <v>0.0006691499122946794</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04312225187553719</v>
+        <v>0.04313785670929807</v>
       </c>
       <c r="K4" t="n">
         <v>0.01838853525588922</v>
@@ -1458,7 +1458,7 @@
         <v>0.01707435453548843</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04598544317421616</v>
+        <v>0.04599090550486749</v>
       </c>
       <c r="P4" t="n">
         <v>0.0208765227331812</v>
@@ -1479,7 +1479,7 @@
         <v>0.05907992413127931</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0006697764732916549</v>
+        <v>0.0006714080708202641</v>
       </c>
       <c r="W4" t="n">
         <v>0.018021220600451</v>
@@ -1503,13 +1503,13 @@
         <v>0.03705818128345665</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.09437576311847228</v>
+        <v>0.09437904292677847</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1030133581863906</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08276387869824205</v>
+        <v>0.08276784134123334</v>
       </c>
       <c r="AG4" t="n">
         <v>0.02526041335928407</v>
@@ -1575,7 +1575,7 @@
         <v>0.01493088044797698</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01822390958672555</v>
+        <v>0.01822444304150563</v>
       </c>
       <c r="BC4" t="n">
         <v>0.001379212646640884</v>
@@ -1644,10 +1644,10 @@
         <v>0.0009523823065580374</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0005007519335416845</v>
+        <v>0.0005026372354325117</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0005069429790449337</v>
+        <v>0.0005050961900093145</v>
       </c>
       <c r="CA4" t="n">
         <v>0.001263042454127849</v>
@@ -1665,7 +1665,7 @@
         <v>0.002823939585059259</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.01830742367014056</v>
+        <v>0.01830713637224909</v>
       </c>
       <c r="CG4" t="n">
         <v>0.0325823925179633</v>
@@ -1780,7 +1780,7 @@
         <v>0.07803102247546698</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0002040816326530415</v>
+        <v>-0.0002380952380952151</v>
       </c>
       <c r="AG5" t="n">
         <v>0.06970966776414245</v>
@@ -1982,7 +1982,7 @@
         <v>-0.001405942078173788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0007451285754836335</v>
+        <v>-0.000720942828950255</v>
       </c>
       <c r="J6" t="n">
         <v>0.003122011594195539</v>
@@ -2021,7 +2021,7 @@
         <v>0.08738417227133602</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.000720942828950255</v>
+        <v>-0.0007451285754836335</v>
       </c>
       <c r="W6" t="n">
         <v>-0.00949575339117684</v>
@@ -2117,7 +2117,7 @@
         <v>-0.008757548065724135</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.004995610265400293</v>
+        <v>-0.005003514154113538</v>
       </c>
       <c r="BC6" t="n">
         <v>-0.00108841551952564</v>
@@ -2207,7 +2207,7 @@
         <v>-5.991956744537676e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.006006294040352231</v>
+        <v>-0.005982582374212486</v>
       </c>
       <c r="CG6" t="n">
         <v>-0.00797164638982651</v>
@@ -2271,7 +2271,7 @@
         <v>0.004631092045406587</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0161707661827057</v>
+        <v>0.01615530067079726</v>
       </c>
       <c r="P7" t="n">
         <v>0.0064629383208891</v>
@@ -2292,7 +2292,7 @@
         <v>0.1085580431918844</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0002133993909367748</v>
+        <v>-0.0002304061936578616</v>
       </c>
       <c r="W7" t="n">
         <v>0.0007241178856809581</v>
@@ -2542,7 +2542,7 @@
         <v>0.009539431383537935</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04432531297787423</v>
+        <v>0.04434917552957643</v>
       </c>
       <c r="P8" t="n">
         <v>0.02648156946947535</v>
@@ -2728,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
+        <v>-8.826777152533549e-05</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>-9.6278024649335e-05</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>-8.826777152533549e-05</v>
       </c>
       <c r="CA8" t="n">
         <v>0.0006656424414867246</v>
@@ -2798,7 +2798,7 @@
         <v>0.0005064893953783178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1297675899395097</v>
+        <v>0.1298312639286851</v>
       </c>
       <c r="K9" t="n">
         <v>0.0511237733459956</v>
